--- a/price-sam.filled.ok.xlsx
+++ b/price-sam.filled.ok.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Валерій Коростіль\OneDrive\Документи\GitHub\my\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BB2A93E-80F4-4BB5-910E-8171424D2D58}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EA1A8A3-A580-4A2E-9041-D2CA838C2DD5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15150" xr2:uid="{76CD63DD-B582-41E3-B010-ADEC8F91F686}"/>
   </bookViews>
@@ -388,12 +388,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -424,7 +430,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -445,6 +451,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1226,7 +1238,7 @@
       <c r="D10" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="8" t="s">
         <v>22</v>
       </c>
       <c r="F10" s="1" t="s">
@@ -1270,7 +1282,7 @@
       <c r="C11" s="7">
         <v>6754</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="8" t="s">
         <v>24</v>
       </c>
       <c r="E11" s="4" t="s">
@@ -1364,7 +1376,7 @@
       <c r="C13" s="7">
         <v>9845</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="8" t="s">
         <v>27</v>
       </c>
       <c r="E13" s="4" t="s">
@@ -1505,7 +1517,7 @@
       <c r="C16" s="7">
         <v>13970</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="8" t="s">
         <v>31</v>
       </c>
       <c r="E16" s="4" t="s">
@@ -1693,7 +1705,7 @@
       <c r="C20" s="7">
         <v>20570</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="8" t="s">
         <v>38</v>
       </c>
       <c r="E20" s="4" t="s">
@@ -1834,7 +1846,7 @@
       <c r="C23" s="7">
         <v>17105</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="8" t="s">
         <v>43</v>
       </c>
       <c r="E23" s="4" t="s">
@@ -1928,7 +1940,7 @@
       <c r="C25" s="7">
         <v>19855</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="9" t="s">
         <v>43</v>
       </c>
       <c r="E25" s="4" t="s">
@@ -1975,7 +1987,7 @@
       <c r="C26" s="7">
         <v>17985</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="8" t="s">
         <v>48</v>
       </c>
       <c r="E26" s="4" t="s">
@@ -2116,7 +2128,7 @@
       <c r="C29" s="7">
         <v>10945</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="8" t="s">
         <v>53</v>
       </c>
       <c r="E29" s="4" t="s">

--- a/price-sam.filled.ok.xlsx
+++ b/price-sam.filled.ok.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Валерій Коростіль\OneDrive\Документи\GitHub\my\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EA1A8A3-A580-4A2E-9041-D2CA838C2DD5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1103FBB4-412C-4185-9F30-75EF9BC42982}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15150" xr2:uid="{76CD63DD-B582-41E3-B010-ADEC8F91F686}"/>
   </bookViews>
@@ -345,7 +345,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -382,6 +382,14 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
@@ -430,7 +438,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -457,6 +465,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -850,7 +861,7 @@
       <c r="W1" s="2"/>
     </row>
     <row r="2" spans="1:23" ht="60" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="10" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -897,7 +908,7 @@
       <c r="W2" s="2"/>
     </row>
     <row r="3" spans="1:23" ht="60" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="10" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
